--- a/sequences/localizer_conditions_02.xlsx
+++ b/sequences/localizer_conditions_02.xlsx
@@ -504,30 +504,30 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>jacket\jacket_16.jpg</t>
+          <t>bread\bread_03.jpg</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Jacke</t>
+          <t>Brot</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Veste</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -537,7 +537,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
@@ -551,30 +551,30 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>dog\dog_08.jpg</t>
+          <t>hammer\hammer_20.jpg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hund</t>
+          <t>Hammer</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Chien</t>
+          <t>Marteau</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.91</v>
+        <v>1.05</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
@@ -598,30 +598,30 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ball\ball_10.jpg</t>
+          <t>bread\bread_09.jpg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ball</t>
+          <t>Brot</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Ballon</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -631,7 +631,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1.03</v>
+        <v>0.98</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
@@ -645,30 +645,30 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>bread\bread_11.jpg</t>
+          <t>hammer\hammer_34.jpg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Brot</t>
+          <t>Hammer</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Marteau</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -678,7 +678,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2</v>
+        <v>0.88</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -692,30 +692,30 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>jacket\jacket_15.jpg</t>
+          <t>ball\ball_04.jpg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Jacke</t>
+          <t>Ball</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Veste</t>
+          <t>Ballon</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -725,7 +725,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.87</v>
+        <v>1.19</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
@@ -739,30 +739,30 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>dog\dog_09.jpg</t>
+          <t>hand\hand_24.jpg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hund</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Chien</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -772,7 +772,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.12</v>
+        <v>0.96</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
@@ -786,30 +786,30 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>flower\flower_03.jpg</t>
+          <t>bicycle\bicycle_18.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Blume</t>
+          <t>Fahrrad</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Fleur</t>
+          <t>Vélo</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -819,7 +819,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1.23</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
@@ -833,30 +833,30 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>house\house_14.jpg</t>
+          <t>hand\hand_22.jpg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Haus</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Maison</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -866,7 +866,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8</v>
+        <v>0.93</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
@@ -880,30 +880,30 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>dog\dog_13.jpg</t>
+          <t>flower\flower_06.jpg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Blume</t>
+          <t>Ball</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Fleur</t>
+          <t>Ballon</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -913,7 +913,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0.82</v>
+        <v>0.77</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -935,30 +935,30 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>house</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>chair\chair_20.jpg</t>
+          <t>house\house_12.jpg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>house</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Stuhl</t>
+          <t>Haus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Chaise</t>
+          <t>Maison</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -968,7 +968,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
@@ -982,30 +982,30 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ball\ball_16.jpg</t>
+          <t>dog\dog_22.jpg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ball</t>
+          <t>Hund</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Ballon</t>
+          <t>Chien</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.9</v>
+        <v>1.21</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
@@ -1029,30 +1029,30 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>bicycle\bicycle_13.jpg</t>
+          <t>chair\chair_08.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fahrrad</t>
+          <t>Stuhl</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Vélo</t>
+          <t>Chaise</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1076,30 +1076,30 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ball\ball_12.jpg</t>
+          <t>flower\flower_33.jpg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ball</t>
+          <t>Blume</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Ballon</t>
+          <t>Fleur</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1109,7 +1109,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.84</v>
+        <v>1.04</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
@@ -1123,30 +1123,30 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>bread\bread_01.jpg</t>
+          <t>house\house_39.jpg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Brot</t>
+          <t>Haus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Maison</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1156,7 +1156,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
@@ -1170,43 +1170,51 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>flower\flower_06.jpg</t>
+          <t>ball\ball_32.jpg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Blume</t>
+          <t>Fahrrad</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Fleur</t>
+          <t>Vélo</t>
         </is>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+        <v>0.97</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1217,30 +1225,30 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>jacket\jacket_03.jpg</t>
+          <t>chair\chair_23.jpg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Jacke</t>
+          <t>Stuhl</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Veste</t>
+          <t>Chaise</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1250,7 +1258,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
@@ -1264,51 +1272,43 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>bread\bread_06.jpg</t>
+          <t>dog\dog_30.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fahrrad</t>
+          <t>Hund</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Vélo</t>
+          <t>Chien</t>
         </is>
       </c>
       <c r="I18" t="n">
         <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+        <v>1.21</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1319,30 +1319,30 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>hand\hand_08.jpg</t>
+          <t>jacket\jacket_02.jpg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Jacke</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Veste</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -1352,7 +1352,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1.09</v>
+        <v>0.8</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
@@ -1366,30 +1366,30 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ball\ball_09.jpg</t>
+          <t>bicycle\bicycle_08.jpg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ball</t>
+          <t>Fahrrad</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Ballon</t>
+          <t>Vélo</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -1399,7 +1399,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.95</v>
+        <v>1.14</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
@@ -1413,30 +1413,30 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>bicycle\bicycle_09.jpg</t>
+          <t>jacket\jacket_07.jpg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fahrrad</t>
+          <t>Jacke</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Vélo</t>
+          <t>Veste</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -1446,7 +1446,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
@@ -1468,43 +1468,35 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>dog\dog_12.jpg</t>
+          <t>dog\dog_33.jpg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ball</t>
+          <t>Hund</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Ballon</t>
+          <t>Chien</t>
         </is>
       </c>
       <c r="I22" t="n">
         <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+        <v>0.82</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1515,30 +1507,30 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>house\house_01.jpg</t>
+          <t>hand\hand_02.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Haus</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Maison</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -1548,7 +1540,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>1.06</v>
+        <v>0.86</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
@@ -1562,51 +1554,43 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ball\ball_03.jpg</t>
+          <t>bread\bread_06.jpg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fahrrad</t>
+          <t>Brot</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Vélo</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="I24" t="n">
         <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+        <v>0.89</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1617,30 +1601,30 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>house\house_07.jpg</t>
+          <t>chair\chair_18.jpg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Haus</t>
+          <t>Stuhl</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Maison</t>
+          <t>Chaise</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -1650,7 +1634,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>1.17</v>
+        <v>0.86</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
@@ -1664,30 +1648,30 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>hammer\hammer_14.jpg</t>
+          <t>bread\bread_21.jpg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hammer</t>
+          <t>Brot</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Marteau</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -1697,7 +1681,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0.82</v>
+        <v>1.16</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
@@ -1719,7 +1703,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>flower\flower_07.jpg</t>
+          <t>flower\flower_22.jpg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1744,7 +1728,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>1.22</v>
+        <v>1.02</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
@@ -1758,30 +1742,30 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>house</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>hammer\hammer_16.jpg</t>
+          <t>house\house_37.jpg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>house</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hammer</t>
+          <t>Haus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Marteau</t>
+          <t>Maison</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -1791,7 +1775,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
@@ -1805,30 +1789,30 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>bread\bread_02.jpg</t>
+          <t>dog\dog_24.jpg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Brot</t>
+          <t>Hund</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Chien</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -1838,7 +1822,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0.89</v>
+        <v>1.16</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
@@ -1852,30 +1836,30 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>jacket\jacket_04.jpg</t>
+          <t>chair\chair_12.jpg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Jacke</t>
+          <t>Stuhl</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Veste</t>
+          <t>Chaise</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -1885,7 +1869,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>1.14</v>
+        <v>0.87</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
@@ -1899,43 +1883,51 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>flower\flower_16.jpg</t>
+          <t>bicycle\bicycle_39.jpg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Blume</t>
+          <t>Hammer</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Fleur</t>
+          <t>Marteau</t>
         </is>
       </c>
       <c r="I31" t="n">
         <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+        <v>0.88</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1946,30 +1938,30 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>bread\bread_04.jpg</t>
+          <t>flower\flower_25.jpg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Brot</t>
+          <t>Blume</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Fleur</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -1979,7 +1971,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.87</v>
+        <v>1.09</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
@@ -1993,30 +1985,30 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>house</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>chair\chair_19.jpg</t>
+          <t>house\house_04.jpg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>house</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Stuhl</t>
+          <t>Haus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Chaise</t>
+          <t>Maison</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -2026,7 +2018,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.87</v>
+        <v>1.01</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
@@ -2040,30 +2032,30 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>house\house_11.jpg</t>
+          <t>bicycle\bicycle_14.jpg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Haus</t>
+          <t>Fahrrad</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Maison</t>
+          <t>Vélo</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -2073,7 +2065,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -2087,30 +2079,30 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>hand\hand_12.jpg</t>
+          <t>hammer\hammer_05.jpg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Hammer</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Marteau</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -2120,7 +2112,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0.97</v>
+        <v>1.17</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
@@ -2134,30 +2126,30 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>dog\dog_02.jpg</t>
+          <t>ball\ball_20.jpg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hund</t>
+          <t>Ball</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Chien</t>
+          <t>Ballon</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -2167,7 +2159,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0.92</v>
+        <v>1.12</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
@@ -2181,30 +2173,30 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>flower\flower_09.jpg</t>
+          <t>hammer\hammer_14.jpg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Blume</t>
+          <t>Hammer</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Fleur</t>
+          <t>Marteau</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -2214,7 +2206,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>1.05</v>
+        <v>0.96</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
@@ -2228,30 +2220,30 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>bicycle\bicycle_10.jpg</t>
+          <t>hand\hand_20.jpg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fahrrad</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Vélo</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -2261,7 +2253,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
@@ -2275,30 +2267,30 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>chair\chair_04.jpg</t>
+          <t>jacket\jacket_36.jpg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Stuhl</t>
+          <t>Jacke</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Chaise</t>
+          <t>Veste</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -2308,7 +2300,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>1.19</v>
+        <v>0.86</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
@@ -2322,30 +2314,30 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>jacket\jacket_06.jpg</t>
+          <t>ball\ball_14.jpg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Jacke</t>
+          <t>Ball</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Veste</t>
+          <t>Ballon</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -2355,7 +2347,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
@@ -2369,43 +2361,51 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>house\house_04.jpg</t>
+          <t>jacket\jacket_12.jpg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Haus</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Maison</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="I41" t="n">
         <v>1</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
+        <v>1.17</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2416,43 +2416,51 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>hammer\hammer_04.jpg</t>
+          <t>hand\hand_23.jpg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hammer</t>
+          <t>Fahrrad</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Marteau</t>
+          <t>Vélo</t>
         </is>
       </c>
       <c r="I42" t="n">
         <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
+        <v>1.09</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2463,30 +2471,30 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>chair\chair_10.jpg</t>
+          <t>hammer\hammer_17.jpg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Stuhl</t>
+          <t>Hammer</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Chaise</t>
+          <t>Marteau</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -2496,7 +2504,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
@@ -2510,30 +2518,30 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>bicycle\bicycle_03.jpg</t>
+          <t>flower\flower_02.jpg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fahrrad</t>
+          <t>Blume</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Vélo</t>
+          <t>Fleur</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -2543,7 +2551,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>1.13</v>
+        <v>0.82</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
@@ -2557,30 +2565,30 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>chair\chair_18.jpg</t>
+          <t>dog\dog_31.jpg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Stuhl</t>
+          <t>Hund</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Chaise</t>
+          <t>Chien</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -2590,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0.97</v>
+        <v>1.24</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
@@ -2604,51 +2612,43 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>hand\hand_04.jpg</t>
+          <t>chair\chair_32.jpg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fahrrad</t>
+          <t>Stuhl</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Vélo</t>
+          <t>Chaise</t>
         </is>
       </c>
       <c r="I46" t="n">
         <v>1</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+        <v>0.99</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2659,30 +2659,30 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>house</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>hammer\hammer_09.jpg</t>
+          <t>house\house_27.jpg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>house</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hammer</t>
+          <t>Haus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Marteau</t>
+          <t>Maison</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -2692,7 +2692,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>1.24</v>
+        <v>0.79</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
@@ -2706,30 +2706,30 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>bicycle\bicycle_01.jpg</t>
+          <t>jacket\jacket_01.jpg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fahrrad</t>
+          <t>Jacke</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Vélo</t>
+          <t>Veste</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -2739,7 +2739,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>1.21</v>
+        <v>0.86</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
@@ -2753,30 +2753,30 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>hand\hand_06.jpg</t>
+          <t>bicycle\bicycle_22.jpg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Fahrrad</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Vélo</t>
         </is>
       </c>
       <c r="I49" t="n">
@@ -2786,7 +2786,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>1.15</v>
+        <v>0.92</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
@@ -2800,30 +2800,30 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>hammer\hammer_08.jpg</t>
+          <t>bread\bread_02.jpg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hammer</t>
+          <t>Brot</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Marteau</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -2833,7 +2833,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
@@ -2847,30 +2847,30 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>hand\hand_13.jpg</t>
+          <t>ball\ball_38.jpg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Ball</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Ballon</t>
         </is>
       </c>
       <c r="I51" t="n">
@@ -2880,7 +2880,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
@@ -2894,30 +2894,30 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>bread\bread_12.jpg</t>
+          <t>jacket\jacket_15.jpg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Brot</t>
+          <t>Jacke</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Veste</t>
         </is>
       </c>
       <c r="I52" t="n">
@@ -2927,7 +2927,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>0.85</v>
+        <v>1.01</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
@@ -2941,30 +2941,30 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>house\house_16.jpg</t>
+          <t>ball\ball_05.jpg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Haus</t>
+          <t>Ball</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Maison</t>
+          <t>Ballon</t>
         </is>
       </c>
       <c r="I53" t="n">
@@ -2974,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>0.99</v>
+        <v>1.13</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
@@ -2988,30 +2988,30 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>flower\flower_01.jpg</t>
+          <t>bicycle\bicycle_30.jpg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Blume</t>
+          <t>Fahrrad</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Fleur</t>
+          <t>Vélo</t>
         </is>
       </c>
       <c r="I54" t="n">
@@ -3021,7 +3021,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>0.9</v>
+        <v>1.21</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
@@ -3035,51 +3035,43 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>hammer\hammer_03.jpg</t>
+          <t>dog\dog_06.jpg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Haus</t>
+          <t>Hund</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Maison</t>
+          <t>Chien</t>
         </is>
       </c>
       <c r="I55" t="n">
         <v>1</v>
       </c>
       <c r="J55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+        <v>1.12</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3090,43 +3082,51 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>chair\chair_16.jpg</t>
+          <t>hammer\hammer_13.jpg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Stuhl</t>
+          <t>Jacke</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Chaise</t>
+          <t>Veste</t>
         </is>
       </c>
       <c r="I56" t="n">
         <v>1</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K56" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
+        <v>1.06</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3137,30 +3137,30 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>bread\bread_14.jpg</t>
+          <t>chair\chair_38.jpg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Brot</t>
+          <t>Stuhl</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Chaise</t>
         </is>
       </c>
       <c r="I57" t="n">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
@@ -3184,30 +3184,30 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>bicycle\bicycle_15.jpg</t>
+          <t>house\house_10.jpg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fahrrad</t>
+          <t>Haus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Vélo</t>
+          <t>Maison</t>
         </is>
       </c>
       <c r="I58" t="n">
@@ -3217,7 +3217,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
@@ -3231,30 +3231,30 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>jacket\jacket_13.jpg</t>
+          <t>bread\bread_30.jpg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Jacke</t>
+          <t>Brot</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Veste</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="I59" t="n">
@@ -3264,7 +3264,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
@@ -3278,15 +3278,15 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>chair\chair_17.jpg</t>
+          <t>flower\flower_39.jpg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3308,21 +3308,13 @@
         <v>1</v>
       </c>
       <c r="J60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+        <v>0.8</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3333,30 +3325,30 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>bread\bread_13.jpg</t>
+          <t>hand\hand_06.jpg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Brot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="I61" t="n">
@@ -3366,7 +3358,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>1.01</v>
+        <v>0.86</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
@@ -3380,30 +3372,30 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>hand\hand_20.jpg</t>
+          <t>chair\chair_26.jpg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Stuhl</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Chaise</t>
         </is>
       </c>
       <c r="I62" t="n">
@@ -3413,7 +3405,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>0.95</v>
+        <v>0.77</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
@@ -3427,30 +3419,30 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>chair\chair_05.jpg</t>
+          <t>bread\bread_14.jpg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Stuhl</t>
+          <t>Brot</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Chaise</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="I63" t="n">
@@ -3460,7 +3452,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>0.77</v>
+        <v>1.25</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
@@ -3474,30 +3466,30 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ball\ball_13.jpg</t>
+          <t>flower\flower_01.jpg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ball</t>
+          <t>Blume</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Ballon</t>
+          <t>Fleur</t>
         </is>
       </c>
       <c r="I64" t="n">
@@ -3507,7 +3499,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
@@ -3521,30 +3513,30 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>dog\dog_18.jpg</t>
+          <t>hammer\hammer_40.jpg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hund</t>
+          <t>Hammer</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Chien</t>
+          <t>Marteau</t>
         </is>
       </c>
       <c r="I65" t="n">
@@ -3554,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>0.78</v>
+        <v>1.19</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
@@ -3568,30 +3560,30 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>bread\bread_19.jpg</t>
+          <t>ball\ball_23.jpg</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Brot</t>
+          <t>Ball</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Ballon</t>
         </is>
       </c>
       <c r="I66" t="n">
@@ -3601,7 +3593,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>0.8</v>
+        <v>1.03</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
@@ -3615,30 +3607,30 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ball\ball_18.jpg</t>
+          <t>chair\chair_28.jpg</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ball</t>
+          <t>Stuhl</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Ballon</t>
+          <t>Chaise</t>
         </is>
       </c>
       <c r="I67" t="n">
@@ -3648,7 +3640,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>1.24</v>
+        <v>0.89</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
@@ -3662,30 +3654,30 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>hand\hand_14.jpg</t>
+          <t>dog\dog_36.jpg</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Hund</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Chien</t>
         </is>
       </c>
       <c r="I68" t="n">
@@ -3695,7 +3687,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>1.25</v>
+        <v>0.91</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
@@ -3709,30 +3701,30 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>chair\chair_03.jpg</t>
+          <t>bread\bread_01.jpg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Stuhl</t>
+          <t>Brot</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Chaise</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="I69" t="n">
@@ -3742,7 +3734,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
@@ -3756,30 +3748,30 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>hand\hand_16.jpg</t>
+          <t>jacket\jacket_27.jpg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Jacke</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Veste</t>
         </is>
       </c>
       <c r="I70" t="n">
@@ -3789,7 +3781,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
@@ -3803,15 +3795,15 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>jacket\jacket_01.jpg</t>
+          <t>bicycle\bicycle_24.jpg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3836,7 +3828,7 @@
         <v>1</v>
       </c>
       <c r="K71" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -3845,7 +3837,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
     </row>
@@ -3858,30 +3850,30 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>bicycle\bicycle_02.jpg</t>
+          <t>hammer\hammer_31.jpg</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fahrrad</t>
+          <t>Hammer</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Vélo</t>
+          <t>Marteau</t>
         </is>
       </c>
       <c r="I72" t="n">
@@ -3891,7 +3883,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0.82</v>
+        <v>1.16</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
@@ -3905,43 +3897,51 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>hand\hand_03.jpg</t>
+          <t>flower\flower_32.jpg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Haus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Maison</t>
         </is>
       </c>
       <c r="I73" t="n">
         <v>1</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K73" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
+        <v>0.98</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -3952,30 +3952,30 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>bicycle\bicycle_08.jpg</t>
+          <t>hand\hand_04.jpg</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fahrrad</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Vélo</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="I74" t="n">
@@ -3985,7 +3985,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
@@ -3999,30 +3999,30 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>jacket\jacket_09.jpg</t>
+          <t>ball\ball_03.jpg</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Jacke</t>
+          <t>Ball</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Veste</t>
+          <t>Ballon</t>
         </is>
       </c>
       <c r="I75" t="n">
@@ -4032,7 +4032,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0.75</v>
+        <v>1.24</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
@@ -4046,30 +4046,30 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>hammer\hammer_06.jpg</t>
+          <t>hand\hand_34.jpg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hammer</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Marteau</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="I76" t="n">
@@ -4079,7 +4079,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>1.05</v>
+        <v>1.24</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
@@ -4093,30 +4093,30 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>bread\bread_03.jpg</t>
+          <t>bicycle\bicycle_09.jpg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Brot</t>
+          <t>Fahrrad</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Vélo</t>
         </is>
       </c>
       <c r="I77" t="n">
@@ -4126,7 +4126,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>0.83</v>
+        <v>0.96</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
@@ -4140,30 +4140,30 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>dog\dog_10.jpg</t>
+          <t>jacket\jacket_10.jpg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hund</t>
+          <t>Jacke</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Chien</t>
+          <t>Veste</t>
         </is>
       </c>
       <c r="I78" t="n">
@@ -4173,7 +4173,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>0.9</v>
+        <v>0.83</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>house\house_05.jpg</t>
+          <t>house\house_35.jpg</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4220,7 +4220,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
@@ -4234,30 +4234,30 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>hammer\hammer_02.jpg</t>
+          <t>dog\dog_34.jpg</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hammer</t>
+          <t>Hund</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Marteau</t>
+          <t>Chien</t>
         </is>
       </c>
       <c r="I80" t="n">
@@ -4267,7 +4267,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>1.09</v>
+        <v>0.79</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
@@ -4281,30 +4281,30 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>house</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>jacket\jacket_07.jpg</t>
+          <t>house\house_31.jpg</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>house</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Jacke</t>
+          <t>Haus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Veste</t>
+          <t>Maison</t>
         </is>
       </c>
       <c r="I81" t="n">
@@ -4314,7 +4314,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>1.05</v>
+        <v>0.86</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
@@ -4328,30 +4328,30 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>bicycle\bicycle_11.jpg</t>
+          <t>ball\ball_25.jpg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Fahrrad</t>
+          <t>Ball</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Vélo</t>
+          <t>Ballon</t>
         </is>
       </c>
       <c r="I82" t="n">
@@ -4361,7 +4361,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>0.85</v>
+        <v>1.18</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
@@ -4375,30 +4375,30 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>flower\flower_18.jpg</t>
+          <t>dog\dog_35.jpg</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Blume</t>
+          <t>Hund</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Fleur</t>
+          <t>Chien</t>
         </is>
       </c>
       <c r="I83" t="n">
@@ -4408,7 +4408,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr"/>
@@ -4430,35 +4430,43 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>chair\chair_15.jpg</t>
+          <t>chair\chair_25.jpg</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Stuhl</t>
+          <t>Jacke</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Chaise</t>
+          <t>Veste</t>
         </is>
       </c>
       <c r="I84" t="n">
         <v>1</v>
       </c>
       <c r="J84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K84" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
+        <v>0.76</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -4469,30 +4477,30 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>jacket\jacket_08.jpg</t>
+          <t>flower\flower_19.jpg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Jacke</t>
+          <t>Blume</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Veste</t>
+          <t>Fleur</t>
         </is>
       </c>
       <c r="I85" t="n">
@@ -4502,7 +4510,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>1.06</v>
+        <v>0.8</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr"/>
@@ -4516,30 +4524,30 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>hand\hand_17.jpg</t>
+          <t>chair\chair_05.jpg</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Stuhl</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Chaise</t>
         </is>
       </c>
       <c r="I86" t="n">
@@ -4549,7 +4557,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>0.82</v>
+        <v>1.04</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr"/>
@@ -4571,7 +4579,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>hammer\hammer_12.jpg</t>
+          <t>hammer\hammer_30.jpg</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4596,7 +4604,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>0.84</v>
+        <v>1.24</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr"/>
@@ -4610,30 +4618,30 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>dog\dog_17.jpg</t>
+          <t>hand\hand_15.jpg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hund</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Chien</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="I88" t="n">
@@ -4643,7 +4651,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr"/>
@@ -4657,30 +4665,30 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>bicycle\bicycle_05.jpg</t>
+          <t>bread\bread_25.jpg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Fahrrad</t>
+          <t>Brot</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Vélo</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="I89" t="n">
@@ -4690,7 +4698,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0.98</v>
+        <v>1.08</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
@@ -4704,30 +4712,30 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>hammer\hammer_07.jpg</t>
+          <t>flower\flower_13.jpg</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hammer</t>
+          <t>Blume</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Marteau</t>
+          <t>Fleur</t>
         </is>
       </c>
       <c r="I90" t="n">
@@ -4737,7 +4745,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr"/>
@@ -4751,30 +4759,30 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>house\house_10.jpg</t>
+          <t>bread\bread_10.jpg</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Haus</t>
+          <t>Brot</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Maison</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="I91" t="n">
@@ -4784,7 +4792,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>1.22</v>
+        <v>0.75</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
@@ -4798,30 +4806,30 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>dog\dog_11.jpg</t>
+          <t>hammer\hammer_39.jpg</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hund</t>
+          <t>Hammer</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Chien</t>
+          <t>Marteau</t>
         </is>
       </c>
       <c r="I92" t="n">
@@ -4831,7 +4839,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
@@ -4845,30 +4853,30 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>flower\flower_08.jpg</t>
+          <t>bicycle\bicycle_21.jpg</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Blume</t>
+          <t>Fahrrad</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Fleur</t>
+          <t>Vélo</t>
         </is>
       </c>
       <c r="I93" t="n">
@@ -4878,7 +4886,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
@@ -4892,43 +4900,51 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>ball\ball_14.jpg</t>
+          <t>house\house_13.jpg</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ball</t>
+          <t>Blume</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Ballon</t>
+          <t>Fleur</t>
         </is>
       </c>
       <c r="I94" t="n">
         <v>1</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K94" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
+        <v>0.91</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -4939,30 +4955,30 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>house\house_15.jpg</t>
+          <t>jacket\jacket_08.jpg</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Haus</t>
+          <t>Jacke</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Maison</t>
+          <t>Veste</t>
         </is>
       </c>
       <c r="I95" t="n">
@@ -4972,7 +4988,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>0.77</v>
+        <v>1.16</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr"/>
@@ -4986,30 +5002,30 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>ball\ball_05.jpg</t>
+          <t>dog\dog_09.jpg</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Ball</t>
+          <t>Hund</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Ballon</t>
+          <t>Chien</t>
         </is>
       </c>
       <c r="I96" t="n">
@@ -5019,7 +5035,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>0.93</v>
+        <v>0.86</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr"/>
@@ -5033,30 +5049,30 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>flower\flower_04.jpg</t>
+          <t>hand\hand_31.jpg</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Blume</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Fleur</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="I97" t="n">
@@ -5066,7 +5082,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>0.95</v>
+        <v>1.14</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr"/>
@@ -5080,30 +5096,30 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>dog\dog_01.jpg</t>
+          <t>house\house_40.jpg</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hund</t>
+          <t>Haus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Chien</t>
+          <t>Maison</t>
         </is>
       </c>
       <c r="I98" t="n">
@@ -5113,7 +5129,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>0.93</v>
+        <v>1.18</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr"/>
@@ -5127,30 +5143,30 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>ball\ball_06.jpg</t>
+          <t>jacket\jacket_06.jpg</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ball</t>
+          <t>Jacke</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Ballon</t>
+          <t>Veste</t>
         </is>
       </c>
       <c r="I99" t="n">
@@ -5160,7 +5176,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>0.97</v>
+        <v>1.09</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
@@ -5174,30 +5190,30 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>flower\flower_12.jpg</t>
+          <t>ball\ball_08.jpg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Blume</t>
+          <t>Ball</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Fleur</t>
+          <t>Ballon</t>
         </is>
       </c>
       <c r="I100" t="n">
@@ -5207,7 +5223,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr"/>
@@ -5221,30 +5237,30 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>house\house_06.jpg</t>
+          <t>bicycle\bicycle_16.jpg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Haus</t>
+          <t>Fahrrad</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Maison</t>
+          <t>Vélo</t>
         </is>
       </c>
       <c r="I101" t="n">
@@ -5254,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
@@ -5268,30 +5284,30 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>hammer\hammer_01.jpg</t>
+          <t>chair\chair_20.jpg</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hammer</t>
+          <t>Stuhl</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Marteau</t>
+          <t>Chaise</t>
         </is>
       </c>
       <c r="I102" t="n">
@@ -5301,7 +5317,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>0.83</v>
+        <v>1.05</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr"/>
@@ -5315,30 +5331,30 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>bicycle\bicycle_12.jpg</t>
+          <t>flower\flower_37.jpg</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Fahrrad</t>
+          <t>Blume</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Vélo</t>
+          <t>Fleur</t>
         </is>
       </c>
       <c r="I103" t="n">
@@ -5348,7 +5364,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>1.21</v>
+        <v>0.79</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr"/>
@@ -5362,30 +5378,30 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>hand\hand_15.jpg</t>
+          <t>dog\dog_27.jpg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Hund</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Chien</t>
         </is>
       </c>
       <c r="I104" t="n">
@@ -5395,7 +5411,7 @@
         <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr"/>
@@ -5409,43 +5425,51 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>ball\ball_01.jpg</t>
+          <t>chair\chair_13.jpg</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ball</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Ballon</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="I105" t="n">
         <v>1</v>
       </c>
       <c r="J105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K105" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
+        <v>0.91</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -5456,30 +5480,30 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>dog\dog_07.jpg</t>
+          <t>house\house_09.jpg</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hund</t>
+          <t>Haus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Chien</t>
+          <t>Maison</t>
         </is>
       </c>
       <c r="I106" t="n">
@@ -5489,7 +5513,7 @@
         <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.93</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr"/>
@@ -5503,30 +5527,30 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>flower\flower_14.jpg</t>
+          <t>bread\bread_22.jpg</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Blume</t>
+          <t>Brot</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Fleur</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="I107" t="n">
@@ -5536,7 +5560,7 @@
         <v>0</v>
       </c>
       <c r="K107" t="n">
-        <v>1.22</v>
+        <v>0.89</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr"/>
@@ -5550,30 +5574,30 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>chair\chair_12.jpg</t>
+          <t>bicycle\bicycle_19.jpg</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Stuhl</t>
+          <t>Fahrrad</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Chaise</t>
+          <t>Vélo</t>
         </is>
       </c>
       <c r="I108" t="n">
@@ -5583,7 +5607,7 @@
         <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr"/>
@@ -5597,43 +5621,51 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>ball\ball_04.jpg</t>
+          <t>bread\bread_24.jpg</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ball</t>
+          <t>Jacke</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Ballon</t>
+          <t>Veste</t>
         </is>
       </c>
       <c r="I109" t="n">
         <v>1</v>
       </c>
       <c r="J109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K109" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
+        <v>1.09</v>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -5644,30 +5676,30 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>dog\dog_15.jpg</t>
+          <t>house\house_03.jpg</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hund</t>
+          <t>Haus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Chien</t>
+          <t>Maison</t>
         </is>
       </c>
       <c r="I110" t="n">
@@ -5677,7 +5709,7 @@
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr"/>
@@ -5699,7 +5731,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>hammer\hammer_18.jpg</t>
+          <t>hammer\hammer_25.jpg</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5724,7 +5756,7 @@
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>0.87</v>
+        <v>1.18</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr"/>
@@ -5738,30 +5770,30 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>hand\hand_10.jpg</t>
+          <t>flower\flower_04.jpg</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Blume</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Fleur</t>
         </is>
       </c>
       <c r="I112" t="n">
@@ -5771,7 +5803,7 @@
         <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>0.85</v>
+        <v>1.19</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr"/>
@@ -5785,30 +5817,30 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>bread\bread_16.jpg</t>
+          <t>ball\ball_09.jpg</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Brot</t>
+          <t>Ball</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Ballon</t>
         </is>
       </c>
       <c r="I113" t="n">
@@ -5818,7 +5850,7 @@
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>0.99</v>
+        <v>0.75</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr"/>
@@ -5832,30 +5864,30 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>house\house_02.jpg</t>
+          <t>jacket\jacket_21.jpg</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Haus</t>
+          <t>Jacke</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Maison</t>
+          <t>Veste</t>
         </is>
       </c>
       <c r="I114" t="n">
@@ -5865,7 +5897,7 @@
         <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>1.19</v>
+        <v>0.98</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr"/>
@@ -5887,7 +5919,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>dog\dog_06.jpg</t>
+          <t>dog\dog_38.jpg</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5912,7 +5944,7 @@
         <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr"/>
@@ -5926,30 +5958,30 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>bicycle\bicycle_18.jpg</t>
+          <t>jacket\jacket_20.jpg</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Fahrrad</t>
+          <t>Jacke</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Vélo</t>
+          <t>Veste</t>
         </is>
       </c>
       <c r="I116" t="n">
@@ -5959,7 +5991,7 @@
         <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr"/>
@@ -5973,30 +6005,30 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>ball\ball_11.jpg</t>
+          <t>hand\hand_28.jpg</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ball</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Ballon</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="I117" t="n">
@@ -6006,7 +6038,7 @@
         <v>0</v>
       </c>
       <c r="K117" t="n">
-        <v>0.84</v>
+        <v>0.96</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr"/>
@@ -6020,30 +6052,30 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>bread\bread_10.jpg</t>
+          <t>ball\ball_16.jpg</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Brot</t>
+          <t>Ball</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Ballon</t>
         </is>
       </c>
       <c r="I118" t="n">
@@ -6053,7 +6085,7 @@
         <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>1.25</v>
+        <v>0.99</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr"/>
@@ -6067,30 +6099,30 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>hand\hand_01.jpg</t>
+          <t>bicycle\bicycle_28.jpg</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Fahrrad</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Vélo</t>
         </is>
       </c>
       <c r="I119" t="n">
@@ -6100,7 +6132,7 @@
         <v>0</v>
       </c>
       <c r="K119" t="n">
-        <v>0.8</v>
+        <v>1.07</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr"/>
@@ -6114,30 +6146,30 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>ball\ball_08.jpg</t>
+          <t>hand\hand_11.jpg</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Ball</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Ballon</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="I120" t="n">
@@ -6147,7 +6179,7 @@
         <v>0</v>
       </c>
       <c r="K120" t="n">
-        <v>1.15</v>
+        <v>0.87</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr"/>
@@ -6161,30 +6193,30 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>chair\chair_11.jpg</t>
+          <t>hammer\hammer_37.jpg</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Stuhl</t>
+          <t>Hammer</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Chaise</t>
+          <t>Marteau</t>
         </is>
       </c>
       <c r="I121" t="n">
@@ -6194,7 +6226,7 @@
         <v>0</v>
       </c>
       <c r="K121" t="n">
-        <v>0.88</v>
+        <v>1.09</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr"/>
@@ -6216,35 +6248,43 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>jacket\jacket_10.jpg</t>
+          <t>jacket\jacket_34.jpg</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>house</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Jacke</t>
+          <t>Haus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Veste</t>
+          <t>Maison</t>
         </is>
       </c>
       <c r="I122" t="n">
         <v>1</v>
       </c>
       <c r="J122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K122" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr"/>
+        <v>1.15</v>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -6255,30 +6295,30 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>house\house_08.jpg</t>
+          <t>bread\bread_11.jpg</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Haus</t>
+          <t>Brot</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Maison</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="I123" t="n">
@@ -6288,7 +6328,7 @@
         <v>0</v>
       </c>
       <c r="K123" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr"/>
@@ -6302,30 +6342,30 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>bicycle\bicycle_07.jpg</t>
+          <t>hammer\hammer_33.jpg</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Fahrrad</t>
+          <t>Hammer</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Vélo</t>
+          <t>Marteau</t>
         </is>
       </c>
       <c r="I124" t="n">
@@ -6335,7 +6375,7 @@
         <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>0.78</v>
+        <v>0.85</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr"/>
@@ -6349,15 +6389,15 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>chair\chair_13.jpg</t>
+          <t>bread\bread_12.jpg</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -6379,21 +6419,13 @@
         <v>1</v>
       </c>
       <c r="J125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K125" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+        <v>0.86</v>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -6404,30 +6436,30 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>hammer\hammer_15.jpg</t>
+          <t>ball\ball_10.jpg</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hammer</t>
+          <t>Ball</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Marteau</t>
+          <t>Ballon</t>
         </is>
       </c>
       <c r="I126" t="n">
@@ -6437,7 +6469,7 @@
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr"/>
@@ -6451,30 +6483,30 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>house</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>jacket\jacket_18.jpg</t>
+          <t>house\house_34.jpg</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>house</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Jacke</t>
+          <t>Haus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Veste</t>
+          <t>Maison</t>
         </is>
       </c>
       <c r="I127" t="n">
@@ -6484,7 +6516,7 @@
         <v>0</v>
       </c>
       <c r="K127" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr"/>
@@ -6498,30 +6530,30 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>hammer\hammer_19.jpg</t>
+          <t>bicycle\bicycle_27.jpg</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hammer</t>
+          <t>Fahrrad</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Marteau</t>
+          <t>Vélo</t>
         </is>
       </c>
       <c r="I128" t="n">
@@ -6531,7 +6563,7 @@
         <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>0.98</v>
+        <v>1.12</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr"/>
@@ -6545,30 +6577,30 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>bicycle\bicycle_19.jpg</t>
+          <t>hand\hand_13.jpg</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Fahrrad</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Vélo</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="I129" t="n">
@@ -6578,7 +6610,7 @@
         <v>0</v>
       </c>
       <c r="K129" t="n">
-        <v>1.01</v>
+        <v>0.76</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr"/>
@@ -6592,30 +6624,30 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>jacket\jacket_19.jpg</t>
+          <t>dog\dog_17.jpg</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Jacke</t>
+          <t>Hund</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Veste</t>
+          <t>Chien</t>
         </is>
       </c>
       <c r="I130" t="n">
@@ -6625,7 +6657,7 @@
         <v>0</v>
       </c>
       <c r="K130" t="n">
-        <v>1.19</v>
+        <v>0.9</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr"/>
@@ -6639,30 +6671,30 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>hammer\hammer_17.jpg</t>
+          <t>chair\chair_29.jpg</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hammer</t>
+          <t>Stuhl</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Marteau</t>
+          <t>Chaise</t>
         </is>
       </c>
       <c r="I131" t="n">
@@ -6672,7 +6704,7 @@
         <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr"/>
@@ -6694,7 +6726,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>jacket\jacket_05.jpg</t>
+          <t>jacket\jacket_38.jpg</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -6719,7 +6751,7 @@
         <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>1.21</v>
+        <v>0.8</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr"/>
@@ -6741,7 +6773,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>dog\dog_20.jpg</t>
+          <t>dog\dog_12.jpg</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -6766,7 +6798,7 @@
         <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr"/>
@@ -6780,51 +6812,43 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>bicycle\bicycle_17.jpg</t>
+          <t>hammer\hammer_18.jpg</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Jacke</t>
+          <t>Hammer</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Veste</t>
+          <t>Marteau</t>
         </is>
       </c>
       <c r="I134" t="n">
         <v>1</v>
       </c>
       <c r="J134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="L134" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+        <v>1.17</v>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -6835,51 +6859,43 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>house\house_19.jpg</t>
+          <t>bicycle\bicycle_05.jpg</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Fahrrad</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Vélo</t>
         </is>
       </c>
       <c r="I135" t="n">
         <v>1</v>
       </c>
       <c r="J135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L135" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -6890,43 +6906,51 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>dog\dog_14.jpg</t>
+          <t>ball\ball_12.jpg</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hund</t>
+          <t>Hammer</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Chien</t>
+          <t>Marteau</t>
         </is>
       </c>
       <c r="I136" t="n">
         <v>1</v>
       </c>
       <c r="J136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K136" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr"/>
+        <v>0.93</v>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -6945,7 +6969,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>house\house_20.jpg</t>
+          <t>house\house_28.jpg</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -6970,7 +6994,7 @@
         <v>0</v>
       </c>
       <c r="K137" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr"/>
@@ -6984,30 +7008,30 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>hand\hand_18.jpg</t>
+          <t>flower\flower_16.jpg</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Blume</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Fleur</t>
         </is>
       </c>
       <c r="I138" t="n">
@@ -7017,7 +7041,7 @@
         <v>0</v>
       </c>
       <c r="K138" t="n">
-        <v>1.11</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr"/>
@@ -7031,30 +7055,30 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>chair\chair_01.jpg</t>
+          <t>hand\hand_33.jpg</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Stuhl</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Chaise</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="I139" t="n">
@@ -7064,7 +7088,7 @@
         <v>0</v>
       </c>
       <c r="K139" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" t="inlineStr"/>
@@ -7078,30 +7102,30 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>hand\hand_07.jpg</t>
+          <t>flower\flower_36.jpg</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Blume</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Fleur</t>
         </is>
       </c>
       <c r="I140" t="n">
@@ -7111,7 +7135,7 @@
         <v>0</v>
       </c>
       <c r="K140" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr"/>
@@ -7125,30 +7149,30 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>house\house_13.jpg</t>
+          <t>chair\chair_14.jpg</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Haus</t>
+          <t>Stuhl</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Maison</t>
+          <t>Chaise</t>
         </is>
       </c>
       <c r="I141" t="n">
@@ -7158,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="K141" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr"/>
@@ -7180,7 +7204,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>bread\bread_17.jpg</t>
+          <t>bread\bread_40.jpg</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -7205,7 +7229,7 @@
         <v>0</v>
       </c>
       <c r="K142" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr"/>
@@ -7219,30 +7243,30 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>flower\flower_05.jpg</t>
+          <t>jacket\jacket_31.jpg</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Blume</t>
+          <t>Jacke</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Fleur</t>
+          <t>Veste</t>
         </is>
       </c>
       <c r="I143" t="n">
@@ -7252,7 +7276,7 @@
         <v>0</v>
       </c>
       <c r="K143" t="n">
-        <v>0.97</v>
+        <v>1.21</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr"/>
@@ -7266,30 +7290,30 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>ball\ball_17.jpg</t>
+          <t>bicycle\bicycle_10.jpg</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Ball</t>
+          <t>Fahrrad</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Ballon</t>
+          <t>Vélo</t>
         </is>
       </c>
       <c r="I144" t="n">
@@ -7299,7 +7323,7 @@
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>1.02</v>
+        <v>0.86</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr"/>
@@ -7313,43 +7337,51 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>flower\flower_10.jpg</t>
+          <t>dog\dog_04.jpg</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Blume</t>
+          <t>Jacke</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Fleur</t>
+          <t>Veste</t>
         </is>
       </c>
       <c r="I145" t="n">
         <v>1</v>
       </c>
       <c r="J145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K145" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr"/>
+        <v>1.14</v>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -7360,30 +7392,30 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>bread\bread_08.jpg</t>
+          <t>hammer\hammer_19.jpg</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Brot</t>
+          <t>Hammer</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Marteau</t>
         </is>
       </c>
       <c r="I146" t="n">
@@ -7393,7 +7425,7 @@
         <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr"/>
@@ -7407,30 +7439,30 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>chair\chair_02.jpg</t>
+          <t>hand\hand_29.jpg</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Stuhl</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Chaise</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="I147" t="n">
@@ -7440,7 +7472,7 @@
         <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>0.99</v>
+        <v>1.11</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr"/>
@@ -7454,30 +7486,30 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>bread\bread_20.jpg</t>
+          <t>flower\flower_18.jpg</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Brot</t>
+          <t>Blume</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Fleur</t>
         </is>
       </c>
       <c r="I148" t="n">
@@ -7487,7 +7519,7 @@
         <v>0</v>
       </c>
       <c r="K148" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" t="inlineStr"/>
@@ -7501,30 +7533,30 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>flower\flower_19.jpg</t>
+          <t>ball\ball_40.jpg</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Blume</t>
+          <t>Ball</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Fleur</t>
+          <t>Ballon</t>
         </is>
       </c>
       <c r="I149" t="n">
@@ -7534,7 +7566,7 @@
         <v>0</v>
       </c>
       <c r="K149" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.12</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" t="inlineStr"/>
@@ -7548,30 +7580,30 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>jacket\jacket_02.jpg</t>
+          <t>chair\chair_03.jpg</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Jacke</t>
+          <t>Stuhl</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Veste</t>
+          <t>Chaise</t>
         </is>
       </c>
       <c r="I150" t="n">
@@ -7581,7 +7613,7 @@
         <v>0</v>
       </c>
       <c r="K150" t="n">
-        <v>0.99</v>
+        <v>1.05</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" t="inlineStr"/>
@@ -7595,30 +7627,30 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>flower\flower_02.jpg</t>
+          <t>house\house_19.jpg</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Blume</t>
+          <t>Haus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Fleur</t>
+          <t>Maison</t>
         </is>
       </c>
       <c r="I151" t="n">
@@ -7628,7 +7660,7 @@
         <v>0</v>
       </c>
       <c r="K151" t="n">
-        <v>1.18</v>
+        <v>0.8</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr"/>
@@ -7642,30 +7674,30 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>bread\bread_07.jpg</t>
+          <t>chair\chair_09.jpg</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Brot</t>
+          <t>Stuhl</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Chaise</t>
         </is>
       </c>
       <c r="I152" t="n">
@@ -7675,7 +7707,7 @@
         <v>0</v>
       </c>
       <c r="K152" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" t="inlineStr"/>
@@ -7689,30 +7721,30 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>dog\dog_05.jpg</t>
+          <t>ball\ball_37.jpg</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hund</t>
+          <t>Ball</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Chien</t>
+          <t>Ballon</t>
         </is>
       </c>
       <c r="I153" t="n">
@@ -7722,7 +7754,7 @@
         <v>0</v>
       </c>
       <c r="K153" t="n">
-        <v>1.08</v>
+        <v>0.8</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" t="inlineStr"/>
@@ -7736,15 +7768,15 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>house\house_12.jpg</t>
+          <t>jacket\jacket_28.jpg</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -7766,21 +7798,13 @@
         <v>1</v>
       </c>
       <c r="J154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K154" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="L154" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+        <v>1.17</v>
+      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -7791,30 +7815,30 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>chair\chair_08.jpg</t>
+          <t>hammer\hammer_01.jpg</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Stuhl</t>
+          <t>Hammer</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Chaise</t>
+          <t>Marteau</t>
         </is>
       </c>
       <c r="I155" t="n">
@@ -7824,7 +7848,7 @@
         <v>0</v>
       </c>
       <c r="K155" t="n">
-        <v>1.07</v>
+        <v>0.83</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" t="inlineStr"/>
@@ -7838,30 +7862,30 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>hammer\hammer_13.jpg</t>
+          <t>hand\hand_07.jpg</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hammer</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Marteau</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="I156" t="n">
@@ -7871,7 +7895,7 @@
         <v>0</v>
       </c>
       <c r="K156" t="n">
-        <v>0.75</v>
+        <v>1.09</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" t="inlineStr"/>
@@ -7885,30 +7909,30 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>bicycle\bicycle_16.jpg</t>
+          <t>flower\flower_07.jpg</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Fahrrad</t>
+          <t>Blume</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Vélo</t>
+          <t>Fleur</t>
         </is>
       </c>
       <c r="I157" t="n">
@@ -7918,7 +7942,7 @@
         <v>0</v>
       </c>
       <c r="K157" t="n">
-        <v>0.9</v>
+        <v>1.06</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" t="inlineStr"/>
@@ -7932,30 +7956,30 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>ball\ball_02.jpg</t>
+          <t>house\house_22.jpg</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Ball</t>
+          <t>Haus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Ballon</t>
+          <t>Maison</t>
         </is>
       </c>
       <c r="I158" t="n">
@@ -7965,7 +7989,7 @@
         <v>0</v>
       </c>
       <c r="K158" t="n">
-        <v>0.75</v>
+        <v>1.03</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr"/>
@@ -7979,30 +8003,30 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>bicycle\bicycle_04.jpg</t>
+          <t>bread\bread_15.jpg</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Fahrrad</t>
+          <t>Brot</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Vélo</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="I159" t="n">
@@ -8012,7 +8036,7 @@
         <v>0</v>
       </c>
       <c r="K159" t="n">
-        <v>0.96</v>
+        <v>1.18</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" t="inlineStr"/>
@@ -8026,43 +8050,51 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>chair\chair_06.jpg</t>
+          <t>dog\dog_10.jpg</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Stuhl</t>
+          <t>Ball</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Chaise</t>
+          <t>Ballon</t>
         </is>
       </c>
       <c r="I160" t="n">
         <v>1</v>
       </c>
       <c r="J160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K160" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr"/>
+        <v>1.23</v>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -8073,30 +8105,30 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>dog\dog_19.jpg</t>
+          <t>bicycle\bicycle_13.jpg</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Hund</t>
+          <t>Fahrrad</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Chien</t>
+          <t>Vélo</t>
         </is>
       </c>
       <c r="I161" t="n">
@@ -8106,7 +8138,7 @@
         <v>0</v>
       </c>
       <c r="K161" t="n">
-        <v>1.04</v>
+        <v>0.82</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" t="inlineStr"/>
@@ -8120,30 +8152,30 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>bicycle\bicycle_14.jpg</t>
+          <t>dog\dog_20.jpg</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Fahrrad</t>
+          <t>Hund</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Vélo</t>
+          <t>Chien</t>
         </is>
       </c>
       <c r="I162" t="n">
@@ -8153,7 +8185,7 @@
         <v>0</v>
       </c>
       <c r="K162" t="n">
-        <v>0.8</v>
+        <v>0.93</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" t="inlineStr"/>
@@ -8167,30 +8199,30 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>house\house_18.jpg</t>
+          <t>hand\hand_10.jpg</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Haus</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Maison</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="I163" t="n">
@@ -8200,7 +8232,7 @@
         <v>0</v>
       </c>
       <c r="K163" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr"/>
@@ -8214,43 +8246,51 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>hand\hand_11.jpg</t>
+          <t>bread\bread_33.jpg</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Haus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Maison</t>
         </is>
       </c>
       <c r="I164" t="n">
         <v>1</v>
       </c>
       <c r="J164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K164" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr"/>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -8269,7 +8309,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>dog\dog_16.jpg</t>
+          <t>dog\dog_05.jpg</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -8294,7 +8334,7 @@
         <v>0</v>
       </c>
       <c r="K165" t="n">
-        <v>0.85</v>
+        <v>1.04</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" t="inlineStr"/>
@@ -8308,30 +8348,30 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>hammer\hammer_05.jpg</t>
+          <t>chair\chair_07.jpg</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Hammer</t>
+          <t>Stuhl</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Marteau</t>
+          <t>Chaise</t>
         </is>
       </c>
       <c r="I166" t="n">
@@ -8341,7 +8381,7 @@
         <v>0</v>
       </c>
       <c r="K166" t="n">
-        <v>0.82</v>
+        <v>1.03</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" t="inlineStr"/>
@@ -8355,30 +8395,30 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>hand\hand_09.jpg</t>
+          <t>hammer\hammer_27.jpg</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Hammer</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Marteau</t>
         </is>
       </c>
       <c r="I167" t="n">
@@ -8388,7 +8428,7 @@
         <v>0</v>
       </c>
       <c r="K167" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" t="inlineStr"/>
@@ -8402,30 +8442,30 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>dog\dog_03.jpg</t>
+          <t>flower\flower_11.jpg</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Hund</t>
+          <t>Blume</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Chien</t>
+          <t>Fleur</t>
         </is>
       </c>
       <c r="I168" t="n">
@@ -8435,7 +8475,7 @@
         <v>0</v>
       </c>
       <c r="K168" t="n">
-        <v>0.78</v>
+        <v>0.89</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" t="inlineStr"/>
@@ -8449,30 +8489,30 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>flower\flower_20.jpg</t>
+          <t>bread\bread_05.jpg</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Blume</t>
+          <t>Brot</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Fleur</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="I169" t="n">
@@ -8482,7 +8522,7 @@
         <v>0</v>
       </c>
       <c r="K169" t="n">
-        <v>0.86</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" t="inlineStr"/>
@@ -8496,15 +8536,15 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>bread\bread_05.jpg</t>
+          <t>hammer\hammer_15.jpg</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -8529,7 +8569,7 @@
         <v>1</v>
       </c>
       <c r="K170" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="L170" t="inlineStr">
         <is>
@@ -8538,7 +8578,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
     </row>
@@ -8551,30 +8591,30 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>hammer\hammer_10.jpg</t>
+          <t>jacket\jacket_13.jpg</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hammer</t>
+          <t>Jacke</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Marteau</t>
+          <t>Veste</t>
         </is>
       </c>
       <c r="I171" t="n">
@@ -8584,7 +8624,7 @@
         <v>0</v>
       </c>
       <c r="K171" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" t="inlineStr"/>
@@ -8598,15 +8638,15 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>bicycle\bicycle_20.jpg</t>
+          <t>chair\chair_39.jpg</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -8628,21 +8668,13 @@
         <v>1</v>
       </c>
       <c r="J172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K172" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="L172" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -8653,30 +8685,30 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>house</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>jacket\jacket_20.jpg</t>
+          <t>house\house_24.jpg</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>house</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Jacke</t>
+          <t>Haus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Veste</t>
+          <t>Maison</t>
         </is>
       </c>
       <c r="I173" t="n">
@@ -8686,7 +8718,7 @@
         <v>0</v>
       </c>
       <c r="K173" t="n">
-        <v>1.19</v>
+        <v>1.03</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" t="inlineStr"/>
@@ -8700,30 +8732,30 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>house\house_03.jpg</t>
+          <t>flower\flower_05.jpg</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Haus</t>
+          <t>Blume</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Maison</t>
+          <t>Fleur</t>
         </is>
       </c>
       <c r="I174" t="n">
@@ -8733,7 +8765,7 @@
         <v>0</v>
       </c>
       <c r="K174" t="n">
-        <v>0.96</v>
+        <v>0.87</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr"/>
@@ -8747,51 +8779,43 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>flower\flower_15.jpg</t>
+          <t>ball\ball_18.jpg</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Jacke</t>
+          <t>Ball</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Veste</t>
+          <t>Ballon</t>
         </is>
       </c>
       <c r="I175" t="n">
         <v>1</v>
       </c>
       <c r="J175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K175" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="L175" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -8802,30 +8826,30 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>house\house_17.jpg</t>
+          <t>jacket\jacket_37.jpg</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Haus</t>
+          <t>Jacke</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Maison</t>
+          <t>Veste</t>
         </is>
       </c>
       <c r="I176" t="n">
@@ -8835,7 +8859,7 @@
         <v>0</v>
       </c>
       <c r="K176" t="n">
-        <v>0.83</v>
+        <v>1.21</v>
       </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" t="inlineStr"/>
@@ -8849,30 +8873,30 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>jacket\jacket_12.jpg</t>
+          <t>hand\hand_12.jpg</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Jacke</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Veste</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="I177" t="n">
@@ -8882,7 +8906,7 @@
         <v>0</v>
       </c>
       <c r="K177" t="n">
-        <v>0.83</v>
+        <v>1.11</v>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" t="inlineStr"/>
@@ -8896,30 +8920,30 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>hand\hand_02.jpg</t>
+          <t>bicycle\bicycle_25.jpg</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Fahrrad</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Vélo</t>
         </is>
       </c>
       <c r="I178" t="n">
@@ -8929,7 +8953,7 @@
         <v>0</v>
       </c>
       <c r="K178" t="n">
-        <v>0.85</v>
+        <v>1.21</v>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" t="inlineStr"/>
@@ -8943,30 +8967,30 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>dog\dog_04.jpg</t>
+          <t>ball\ball_34.jpg</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Hund</t>
+          <t>Ball</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Chien</t>
+          <t>Ballon</t>
         </is>
       </c>
       <c r="I179" t="n">
@@ -8976,7 +9000,7 @@
         <v>0</v>
       </c>
       <c r="K179" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="L179" t="inlineStr"/>
       <c r="M179" t="inlineStr"/>
@@ -8990,30 +9014,30 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>ball\ball_19.jpg</t>
+          <t>bicycle\bicycle_29.jpg</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Ball</t>
+          <t>Fahrrad</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Ballon</t>
+          <t>Vélo</t>
         </is>
       </c>
       <c r="I180" t="n">
@@ -9023,7 +9047,7 @@
         <v>0</v>
       </c>
       <c r="K180" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="L180" t="inlineStr"/>
       <c r="M180" t="inlineStr"/>
@@ -9037,30 +9061,30 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>flower\flower_11.jpg</t>
+          <t>house\house_15.jpg</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Blume</t>
+          <t>Haus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Fleur</t>
+          <t>Maison</t>
         </is>
       </c>
       <c r="I181" t="n">
@@ -9070,7 +9094,7 @@
         <v>0</v>
       </c>
       <c r="K181" t="n">
-        <v>0.89</v>
+        <v>1.04</v>
       </c>
       <c r="L181" t="inlineStr"/>
       <c r="M181" t="inlineStr"/>
@@ -9084,30 +9108,30 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>house\house_09.jpg</t>
+          <t>chair\chair_17.jpg</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Haus</t>
+          <t>Stuhl</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Maison</t>
+          <t>Chaise</t>
         </is>
       </c>
       <c r="I182" t="n">
@@ -9117,7 +9141,7 @@
         <v>0</v>
       </c>
       <c r="K182" t="n">
-        <v>0.78</v>
+        <v>0.91</v>
       </c>
       <c r="L182" t="inlineStr"/>
       <c r="M182" t="inlineStr"/>
@@ -9131,43 +9155,51 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>ball\ball_07.jpg</t>
+          <t>house\house_36.jpg</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Ball</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Ballon</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="I183" t="n">
         <v>1</v>
       </c>
       <c r="J183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K183" t="n">
         <v>0.97</v>
       </c>
-      <c r="L183" t="inlineStr"/>
-      <c r="M183" t="inlineStr"/>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -9178,30 +9210,30 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>flower\flower_17.jpg</t>
+          <t>bread\bread_04.jpg</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Blume</t>
+          <t>Brot</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Fleur</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="I184" t="n">
@@ -9211,7 +9243,7 @@
         <v>0</v>
       </c>
       <c r="K184" t="n">
-        <v>1.14</v>
+        <v>0.79</v>
       </c>
       <c r="L184" t="inlineStr"/>
       <c r="M184" t="inlineStr"/>
@@ -9225,30 +9257,30 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>jacket\jacket_14.jpg</t>
+          <t>flower\flower_30.jpg</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Jacke</t>
+          <t>Blume</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Veste</t>
+          <t>Fleur</t>
         </is>
       </c>
       <c r="I185" t="n">
@@ -9258,7 +9290,7 @@
         <v>0</v>
       </c>
       <c r="K185" t="n">
-        <v>1</v>
+        <v>1.24</v>
       </c>
       <c r="L185" t="inlineStr"/>
       <c r="M185" t="inlineStr"/>
@@ -9272,30 +9304,30 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>chair\chair_09.jpg</t>
+          <t>jacket\jacket_29.jpg</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Stuhl</t>
+          <t>Jacke</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Chaise</t>
+          <t>Veste</t>
         </is>
       </c>
       <c r="I186" t="n">
@@ -9305,7 +9337,7 @@
         <v>0</v>
       </c>
       <c r="K186" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.13</v>
       </c>
       <c r="L186" t="inlineStr"/>
       <c r="M186" t="inlineStr"/>
@@ -9319,30 +9351,30 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>bread\bread_15.jpg</t>
+          <t>ball\ball_35.jpg</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Brot</t>
+          <t>Ball</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Ballon</t>
         </is>
       </c>
       <c r="I187" t="n">
@@ -9352,7 +9384,7 @@
         <v>0</v>
       </c>
       <c r="K187" t="n">
-        <v>0.87</v>
+        <v>1.12</v>
       </c>
       <c r="L187" t="inlineStr"/>
       <c r="M187" t="inlineStr"/>
@@ -9366,51 +9398,43 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>hand\hand_05.jpg</t>
+          <t>dog\dog_21.jpg</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Stuhl</t>
+          <t>Hund</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Chaise</t>
+          <t>Chien</t>
         </is>
       </c>
       <c r="I188" t="n">
         <v>1</v>
       </c>
       <c r="J188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K188" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="L188" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="M188" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+        <v>1.02</v>
+      </c>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -9421,15 +9445,15 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>flower\flower_13.jpg</t>
+          <t>bread\bread_19.jpg</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -9451,21 +9475,13 @@
         <v>1</v>
       </c>
       <c r="J189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K189" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L189" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="M189" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+        <v>1.1</v>
+      </c>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -9476,51 +9492,43 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>ball\ball_20.jpg</t>
+          <t>hand\hand_03.jpg</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Hammer</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Marteau</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="I190" t="n">
         <v>1</v>
       </c>
       <c r="J190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K190" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="L190" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+        <v>0.87</v>
+      </c>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -9531,30 +9539,30 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>chair\chair_14.jpg</t>
+          <t>hammer\hammer_38.jpg</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Stuhl</t>
+          <t>Hammer</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Chaise</t>
+          <t>Marteau</t>
         </is>
       </c>
       <c r="I191" t="n">
@@ -9564,7 +9572,7 @@
         <v>0</v>
       </c>
       <c r="K191" t="n">
-        <v>0.86</v>
+        <v>0.92</v>
       </c>
       <c r="L191" t="inlineStr"/>
       <c r="M191" t="inlineStr"/>
@@ -9578,43 +9586,51 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>hammer\hammer_11.jpg</t>
+          <t>hand\hand_17.jpg</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Hammer</t>
+          <t>Hund</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Marteau</t>
+          <t>Chien</t>
         </is>
       </c>
       <c r="I192" t="n">
         <v>1</v>
       </c>
       <c r="J192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K192" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="L192" t="inlineStr"/>
-      <c r="M192" t="inlineStr"/>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -9625,51 +9641,43 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>jacket\jacket_11.jpg</t>
+          <t>flower\flower_24.jpg</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Fahrrad</t>
+          <t>Blume</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Vélo</t>
+          <t>Fleur</t>
         </is>
       </c>
       <c r="I193" t="n">
         <v>1</v>
       </c>
       <c r="J193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K193" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="L193" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="M193" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+        <v>0.89</v>
+      </c>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -9680,30 +9688,30 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>bread\bread_18.jpg</t>
+          <t>bicycle\bicycle_36.jpg</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Brot</t>
+          <t>Fahrrad</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Vélo</t>
         </is>
       </c>
       <c r="I194" t="n">
@@ -9713,7 +9721,7 @@
         <v>0</v>
       </c>
       <c r="K194" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="L194" t="inlineStr"/>
       <c r="M194" t="inlineStr"/>
@@ -9727,30 +9735,30 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>bicycle\bicycle_06.jpg</t>
+          <t>dog\dog_02.jpg</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Fahrrad</t>
+          <t>Hund</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Vélo</t>
+          <t>Chien</t>
         </is>
       </c>
       <c r="I195" t="n">
@@ -9760,7 +9768,7 @@
         <v>0</v>
       </c>
       <c r="K195" t="n">
-        <v>0.95</v>
+        <v>0.79</v>
       </c>
       <c r="L195" t="inlineStr"/>
       <c r="M195" t="inlineStr"/>
@@ -9774,30 +9782,30 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>hand\hand_19.jpg</t>
+          <t>house\house_38.jpg</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Haus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Maison</t>
         </is>
       </c>
       <c r="I196" t="n">
@@ -9807,7 +9815,7 @@
         <v>0</v>
       </c>
       <c r="K196" t="n">
-        <v>0.89</v>
+        <v>1.03</v>
       </c>
       <c r="L196" t="inlineStr"/>
       <c r="M196" t="inlineStr"/>
@@ -9821,30 +9829,30 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>bread\bread_09.jpg</t>
+          <t>chair\chair_21.jpg</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Brot</t>
+          <t>Stuhl</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Chaise</t>
         </is>
       </c>
       <c r="I197" t="n">
@@ -9854,7 +9862,7 @@
         <v>0</v>
       </c>
       <c r="K197" t="n">
-        <v>0.93</v>
+        <v>0.77</v>
       </c>
       <c r="L197" t="inlineStr"/>
       <c r="M197" t="inlineStr"/>
@@ -9868,51 +9876,43 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>hammer\hammer_20.jpg</t>
+          <t>bicycle\bicycle_40.jpg</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Fahrrad</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Vélo</t>
         </is>
       </c>
       <c r="I198" t="n">
         <v>1</v>
       </c>
       <c r="J198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K198" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="L198" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+        <v>1.08</v>
+      </c>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -9923,30 +9923,30 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>jacket\jacket_17.jpg</t>
+          <t>ball\ball_24.jpg</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Jacke</t>
+          <t>Ball</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Veste</t>
+          <t>Ballon</t>
         </is>
       </c>
       <c r="I199" t="n">
@@ -9956,7 +9956,7 @@
         <v>0</v>
       </c>
       <c r="K199" t="n">
-        <v>0.77</v>
+        <v>1.16</v>
       </c>
       <c r="L199" t="inlineStr"/>
       <c r="M199" t="inlineStr"/>
@@ -9970,30 +9970,30 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>chair\chair_07.jpg</t>
+          <t>hammer\hammer_16.jpg</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Stuhl</t>
+          <t>Hammer</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Chaise</t>
+          <t>Marteau</t>
         </is>
       </c>
       <c r="I200" t="n">
@@ -10003,7 +10003,7 @@
         <v>0</v>
       </c>
       <c r="K200" t="n">
-        <v>1.02</v>
+        <v>0.95</v>
       </c>
       <c r="L200" t="inlineStr"/>
       <c r="M200" t="inlineStr"/>
@@ -10017,30 +10017,30 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>ball\ball_15.jpg</t>
+          <t>jacket\jacket_11.jpg</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Ball</t>
+          <t>Jacke</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Ballon</t>
+          <t>Veste</t>
         </is>
       </c>
       <c r="I201" t="n">
@@ -10050,7 +10050,7 @@
         <v>0</v>
       </c>
       <c r="K201" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="L201" t="inlineStr"/>
       <c r="M201" t="inlineStr"/>
